--- a/INSTANCES/instances_xlsx/A_MTN_3/405FL_15A_4.xlsx
+++ b/INSTANCES/instances_xlsx/A_MTN_3/405FL_15A_4.xlsx
@@ -12813,7 +12813,7 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -12847,7 +12847,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -12864,7 +12864,7 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -12881,7 +12881,7 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -12898,7 +12898,7 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -12915,7 +12915,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -12932,7 +12932,7 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -12949,7 +12949,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -12966,7 +12966,7 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -13000,7 +13000,7 @@
         <v>0</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -13017,7 +13017,7 @@
         <v>0</v>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -13034,7 +13034,7 @@
         <v>0</v>
       </c>
       <c r="D15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15">
         <v>1</v>
